--- a/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings website/rock/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings website/rock/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A59900B9-5D62-0C44-9539-F6A254B4FB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF8BC667-0129-D640-BB06-69033851BFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2580" windowWidth="30620" windowHeight="18100" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3280" yWindow="2580" windowWidth="30620" windowHeight="18100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="273">
   <si>
     <t>KINGS OF EWING — SONG TRACKER</t>
   </si>
@@ -231,9 +231,6 @@
     <t>Don't Let Me Down</t>
   </si>
   <si>
-    <t>Miles / Matt</t>
-  </si>
-  <si>
     <t>Don't Look Back In Anger</t>
   </si>
   <si>
@@ -262,9 +259,6 @@
   </si>
   <si>
     <t>F</t>
-  </si>
-  <si>
-    <t>Matt / Miles</t>
   </si>
   <si>
     <t>10s</t>
@@ -910,10 +904,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[m]:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -1747,7 +1742,7 @@
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1942,35 +1937,12 @@
     <xf numFmtId="46" fontId="20" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="18" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2010,10 +1982,10 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2030,15 +2002,6 @@
     </xf>
     <xf numFmtId="165" fontId="21" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2060,6 +2023,45 @@
     </xf>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2620,12 +2622,12 @@
     </row>
     <row r="5" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B5" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="82" t="s">
+      <c r="C5" s="81" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="14" t="s">
@@ -2876,7 +2878,7 @@
         <v>2.1875000000000002E-3</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="14" t="s">
@@ -2937,16 +2939,16 @@
     </row>
     <row r="10" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>30</v>
@@ -2986,16 +2988,16 @@
     </row>
     <row r="11" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>53</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>54</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>30</v>
@@ -3049,16 +3051,16 @@
     </row>
     <row r="12" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>55</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>56</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>30</v>
@@ -3074,7 +3076,7 @@
         <v>32</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K12" s="14"/>
       <c r="L12" s="16" t="s">
@@ -3106,32 +3108,32 @@
     </row>
     <row r="13" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="14" t="s">
+      <c r="E13" s="13" t="s">
         <v>59</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>60</v>
       </c>
       <c r="F13" s="67">
         <v>2.3032407407407407E-3</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14" t="s">
         <v>32</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K13" s="14"/>
       <c r="L13" s="12"/>
@@ -3157,7 +3159,7 @@
     </row>
     <row r="14" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B14" s="48" t="s">
         <v>2</v>
@@ -3166,7 +3168,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>30</v>
@@ -3204,7 +3206,7 @@
     </row>
     <row r="15" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>2</v>
@@ -3213,7 +3215,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>30</v>
@@ -3275,7 +3277,7 @@
     </row>
     <row r="16" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>2</v>
@@ -3284,7 +3286,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>30</v>
@@ -3336,7 +3338,7 @@
     </row>
     <row r="17" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>2</v>
@@ -3345,10 +3347,10 @@
         <v>3</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F17" s="67">
         <v>1.9328703703703704E-3</v>
@@ -3361,7 +3363,7 @@
         <v>32</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K17" s="14"/>
       <c r="L17" s="12"/>
@@ -3385,7 +3387,7 @@
     </row>
     <row r="18" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>2</v>
@@ -3394,7 +3396,7 @@
         <v>3</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>30</v>
@@ -3410,7 +3412,7 @@
         <v>32</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K18" s="14"/>
       <c r="L18" s="16" t="s">
@@ -3446,7 +3448,7 @@
     </row>
     <row r="19" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>2</v>
@@ -3455,7 +3457,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>30</v>
@@ -3471,7 +3473,7 @@
         <v>32</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K19" s="14"/>
       <c r="L19" s="16" t="s">
@@ -3501,7 +3503,7 @@
     </row>
     <row r="20" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>2</v>
@@ -3510,7 +3512,7 @@
         <v>3</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>30</v>
@@ -3564,7 +3566,7 @@
     </row>
     <row r="21" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>2</v>
@@ -3573,7 +3575,7 @@
         <v>3</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>30</v>
@@ -3582,7 +3584,7 @@
         <v>2.5115740740740741E-3</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
@@ -3611,7 +3613,7 @@
     </row>
     <row r="22" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>2</v>
@@ -3620,7 +3622,7 @@
         <v>3</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>30</v>
@@ -3636,7 +3638,7 @@
         <v>32</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K22" s="14"/>
       <c r="L22" s="16" t="s">
@@ -3688,7 +3690,7 @@
     </row>
     <row r="23" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B23" s="48" t="s">
         <v>2</v>
@@ -3697,7 +3699,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>30</v>
@@ -3751,14 +3753,14 @@
     </row>
     <row r="24" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="50"/>
       <c r="D24" s="14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>30</v>
@@ -3774,7 +3776,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K24" s="14"/>
       <c r="L24" s="14" t="s">
@@ -3812,7 +3814,7 @@
     </row>
     <row r="25" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>2</v>
@@ -3821,7 +3823,7 @@
         <v>3</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E25" s="13" t="s">
         <v>30</v>
@@ -3879,7 +3881,7 @@
     </row>
     <row r="26" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>2</v>
@@ -3888,7 +3890,7 @@
         <v>3</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>30</v>
@@ -3926,7 +3928,7 @@
     </row>
     <row r="27" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>2</v>
@@ -3935,7 +3937,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>30</v>
@@ -3977,7 +3979,7 @@
     </row>
     <row r="28" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>2</v>
@@ -3986,7 +3988,7 @@
         <v>3</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E28" s="13" t="s">
         <v>30</v>
@@ -4002,7 +4004,7 @@
         <v>32</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K28" s="14"/>
       <c r="L28" s="16" t="s">
@@ -4032,7 +4034,7 @@
     </row>
     <row r="29" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>2</v>
@@ -4041,7 +4043,7 @@
         <v>3</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>30</v>
@@ -4101,7 +4103,7 @@
     </row>
     <row r="30" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>2</v>
@@ -4110,7 +4112,7 @@
         <v>3</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>30</v>
@@ -4176,7 +4178,7 @@
     </row>
     <row r="31" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>2</v>
@@ -4227,7 +4229,7 @@
     </row>
     <row r="32" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>2</v>
@@ -4236,7 +4238,7 @@
         <v>3</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>30</v>
@@ -4245,7 +4247,7 @@
         <v>3.2291666666666666E-3</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="14" t="s">
@@ -4286,7 +4288,7 @@
     </row>
     <row r="33" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>2</v>
@@ -4295,10 +4297,10 @@
         <v>3</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F33" s="67">
         <v>2.9513888888888888E-3</v>
@@ -4311,7 +4313,7 @@
         <v>32</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K33" s="14"/>
       <c r="L33" s="16" t="s">
@@ -4355,7 +4357,7 @@
     </row>
     <row r="34" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>2</v>
@@ -4364,7 +4366,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E34" s="13" t="s">
         <v>30</v>
@@ -4416,7 +4418,7 @@
     </row>
     <row r="35" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>2</v>
@@ -4425,7 +4427,7 @@
         <v>3</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E35" s="13" t="s">
         <v>30</v>
@@ -4441,7 +4443,7 @@
         <v>32</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K35" s="14"/>
       <c r="L35" s="12"/>
@@ -4479,7 +4481,7 @@
     </row>
     <row r="36" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>2</v>
@@ -4488,7 +4490,7 @@
         <v>3</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>30</v>
@@ -4532,7 +4534,7 @@
     </row>
     <row r="37" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>2</v>
@@ -4541,10 +4543,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F37" s="67">
         <v>3.3680555555555556E-3</v>
@@ -4557,7 +4559,7 @@
         <v>32</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K37" s="14"/>
       <c r="L37" s="16" t="s">
@@ -4595,7 +4597,7 @@
     </row>
     <row r="38" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>2</v>
@@ -4604,7 +4606,7 @@
         <v>3</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>30</v>
@@ -4650,7 +4652,7 @@
     </row>
     <row r="39" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>2</v>
@@ -4659,7 +4661,7 @@
         <v>3</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E39" s="13" t="s">
         <v>30</v>
@@ -4668,7 +4670,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H39" s="14"/>
       <c r="I39" s="14"/>
@@ -4699,7 +4701,7 @@
     </row>
     <row r="40" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>2</v>
@@ -4708,7 +4710,7 @@
         <v>3</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E40" s="13" t="s">
         <v>30</v>
@@ -4746,7 +4748,7 @@
     </row>
     <row r="41" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>2</v>
@@ -4755,7 +4757,7 @@
         <v>3</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E41" s="13" t="s">
         <v>30</v>
@@ -4771,7 +4773,7 @@
         <v>32</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K41" s="14"/>
       <c r="L41" s="12"/>
@@ -4799,7 +4801,7 @@
     </row>
     <row r="42" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>2</v>
@@ -4808,7 +4810,7 @@
         <v>3</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E42" s="13" t="s">
         <v>30</v>
@@ -4856,7 +4858,7 @@
     </row>
     <row r="43" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>2</v>
@@ -4865,7 +4867,7 @@
         <v>3</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E43" s="13" t="s">
         <v>30</v>
@@ -4905,7 +4907,7 @@
     </row>
     <row r="44" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="14" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>2</v>
@@ -4914,7 +4916,7 @@
         <v>3</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E44" s="13" t="s">
         <v>30</v>
@@ -4960,7 +4962,7 @@
     </row>
     <row r="45" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>2</v>
@@ -4969,7 +4971,7 @@
         <v>3</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E45" s="13" t="s">
         <v>30</v>
@@ -5007,7 +5009,7 @@
     </row>
     <row r="46" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="14" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>2</v>
@@ -5016,7 +5018,7 @@
         <v>3</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E46" s="13" t="s">
         <v>30</v>
@@ -5086,19 +5088,19 @@
     </row>
     <row r="47" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B47" s="50"/>
       <c r="C47" s="50"/>
       <c r="D47" s="14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E47" s="13" t="s">
         <v>30</v>
       </c>
       <c r="F47" s="67"/>
       <c r="G47" s="14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H47" s="14"/>
       <c r="I47" s="14"/>
@@ -5127,7 +5129,7 @@
     </row>
     <row r="48" spans="1:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="14" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B48" s="15" t="s">
         <v>2</v>
@@ -5136,7 +5138,7 @@
         <v>3</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E48" s="13" t="s">
         <v>30</v>
@@ -5152,7 +5154,7 @@
         <v>32</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K48" s="14"/>
       <c r="L48" s="16" t="s">
@@ -5348,7 +5350,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -5358,7 +5360,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -5370,7 +5372,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -5378,10 +5380,10 @@
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="40" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C3" s="38" t="s">
         <v>2</v>
@@ -5411,7 +5413,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F4" s="68">
         <v>2.1874999999999998E-3</v>
@@ -5422,7 +5424,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -5442,7 +5444,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -5462,7 +5464,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>2</v>
@@ -5482,7 +5484,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -5502,7 +5504,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>2</v>
@@ -5550,7 +5552,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>2</v>
@@ -5570,7 +5572,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>2</v>
@@ -5590,7 +5592,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>2</v>
@@ -5610,7 +5612,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>2</v>
@@ -5630,7 +5632,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>2</v>
@@ -5650,7 +5652,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>2</v>
@@ -5670,7 +5672,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>2</v>
@@ -5690,7 +5692,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C19" s="38" t="s">
         <v>2</v>
@@ -5716,7 +5718,7 @@
     <row r="21" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34"/>
       <c r="B21" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C21" s="36"/>
       <c r="D21" s="36"/>
@@ -5780,7 +5782,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -5790,7 +5792,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -5802,7 +5804,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -5822,7 +5824,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F3" s="68">
         <v>2.1874999999999998E-3</v>
@@ -5833,7 +5835,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>2</v>
@@ -5853,7 +5855,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -5873,7 +5875,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -5913,7 +5915,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -5933,7 +5935,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>2</v>
@@ -5953,7 +5955,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>2</v>
@@ -5973,7 +5975,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>2</v>
@@ -5993,7 +5995,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>2</v>
@@ -6019,7 +6021,7 @@
     <row r="14" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34"/>
       <c r="B14" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C14" s="36"/>
       <c r="D14" s="36"/>
@@ -6071,7 +6073,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -6081,7 +6083,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -6093,7 +6095,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -6113,7 +6115,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F3" s="68">
         <v>2.1874999999999998E-3</v>
@@ -6124,7 +6126,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>2</v>
@@ -6144,7 +6146,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -6153,7 +6155,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F5" s="68">
         <v>3.2291666666666666E-3</v>
@@ -6164,7 +6166,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -6184,7 +6186,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>2</v>
@@ -6204,7 +6206,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -6224,7 +6226,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>2</v>
@@ -6244,7 +6246,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>2</v>
@@ -6264,7 +6266,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>2</v>
@@ -6284,7 +6286,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>2</v>
@@ -6304,7 +6306,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>2</v>
@@ -6324,7 +6326,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>2</v>
@@ -6344,7 +6346,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>2</v>
@@ -6364,7 +6366,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>2</v>
@@ -6384,7 +6386,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>2</v>
@@ -6404,7 +6406,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>2</v>
@@ -6424,7 +6426,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C19" s="38" t="s">
         <v>2</v>
@@ -6464,7 +6466,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>2</v>
@@ -6484,7 +6486,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>2</v>
@@ -6504,7 +6506,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>2</v>
@@ -6522,7 +6524,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C24" s="38" t="s">
         <v>2</v>
@@ -6542,7 +6544,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C25" s="38" t="s">
         <v>2</v>
@@ -6562,7 +6564,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C26" s="38" t="s">
         <v>2</v>
@@ -6622,7 +6624,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C29" s="38" t="s">
         <v>2</v>
@@ -6642,7 +6644,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="38" t="s">
@@ -6661,7 +6663,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C31" s="38" t="s">
         <v>2</v>
@@ -6681,7 +6683,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C32" s="38" t="s">
         <v>2</v>
@@ -6701,7 +6703,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C33" s="38" t="s">
         <v>2</v>
@@ -6728,7 +6730,7 @@
     <row r="35" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="34"/>
       <c r="B35" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C35" s="36"/>
       <c r="D35" s="36"/>
@@ -6820,7 +6822,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -6830,7 +6832,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -6842,7 +6844,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -6853,7 +6855,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C3" s="38" t="s">
         <v>2</v>
@@ -6882,7 +6884,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F4" s="68">
         <v>2.1874999999999998E-3</v>
@@ -6913,7 +6915,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -6933,7 +6935,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>2</v>
@@ -6954,7 +6956,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -6974,7 +6976,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>2</v>
@@ -6994,7 +6996,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>2</v>
@@ -7014,7 +7016,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>2</v>
@@ -7034,7 +7036,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>2</v>
@@ -7055,7 +7057,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>2</v>
@@ -7075,7 +7077,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>2</v>
@@ -7095,7 +7097,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>2</v>
@@ -7121,7 +7123,7 @@
     <row r="17" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34"/>
       <c r="B17" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
@@ -7179,7 +7181,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -7189,7 +7191,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -7201,7 +7203,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -7221,7 +7223,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F3" s="68">
         <v>2.1874999999999998E-3</v>
@@ -7232,7 +7234,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>2</v>
@@ -7252,7 +7254,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -7272,7 +7274,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -7309,7 +7311,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -7329,7 +7331,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>2</v>
@@ -7349,7 +7351,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>2</v>
@@ -7369,7 +7371,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>2</v>
@@ -7389,7 +7391,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="38" t="s">
@@ -7408,7 +7410,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>2</v>
@@ -7428,7 +7430,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>2</v>
@@ -7449,7 +7451,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>2</v>
@@ -7469,12 +7471,12 @@
         <v>15</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C16" s="39"/>
       <c r="D16" s="39"/>
       <c r="E16" s="25" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F16" s="68"/>
     </row>
@@ -7489,7 +7491,7 @@
     <row r="18" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="34"/>
       <c r="B18" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C18" s="36"/>
       <c r="D18" s="36"/>
@@ -7544,7 +7546,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -7554,7 +7556,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -7566,7 +7568,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -7586,7 +7588,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F3" s="68">
         <v>2.1874999999999998E-3</v>
@@ -7597,7 +7599,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>2</v>
@@ -7617,7 +7619,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -7637,7 +7639,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -7658,7 +7660,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>2</v>
@@ -7678,7 +7680,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -7698,7 +7700,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>2</v>
@@ -7707,7 +7709,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F9" s="68">
         <v>3.2291666666666666E-3</v>
@@ -7735,7 +7737,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>2</v>
@@ -7755,7 +7757,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>2</v>
@@ -7764,7 +7766,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="F12" s="68">
         <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
@@ -7776,7 +7778,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>2</v>
@@ -7796,7 +7798,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>2</v>
@@ -7816,7 +7818,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>2</v>
@@ -7836,7 +7838,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>2</v>
@@ -7856,7 +7858,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>2</v>
@@ -7876,7 +7878,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>2</v>
@@ -7896,7 +7898,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C19" s="39"/>
       <c r="D19" s="38" t="s">
@@ -7915,7 +7917,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C20" s="38" t="s">
         <v>2</v>
@@ -7955,7 +7957,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>2</v>
@@ -7975,7 +7977,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>2</v>
@@ -7995,7 +7997,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C24" s="38" t="s">
         <v>2</v>
@@ -8054,7 +8056,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C27" s="38" t="s">
         <v>2</v>
@@ -8075,7 +8077,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C28" s="38" t="s">
         <v>2</v>
@@ -8095,7 +8097,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C29" s="38" t="s">
         <v>2</v>
@@ -8115,7 +8117,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C30" s="38" t="s">
         <v>2</v>
@@ -8141,7 +8143,7 @@
     <row r="32" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="34"/>
       <c r="B32" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C32" s="36"/>
       <c r="D32" s="36"/>
@@ -8225,7 +8227,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -8235,7 +8237,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -8247,7 +8249,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -8267,7 +8269,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F3" s="68">
         <v>2.1874999999999998E-3</v>
@@ -8278,7 +8280,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>2</v>
@@ -8298,7 +8300,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -8318,7 +8320,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -8339,7 +8341,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>2</v>
@@ -8359,7 +8361,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -8379,7 +8381,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>2</v>
@@ -8388,7 +8390,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="F9" s="68">
         <f>VLOOKUP(B9,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
@@ -8400,7 +8402,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>2</v>
@@ -8420,7 +8422,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>2</v>
@@ -8440,7 +8442,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>2</v>
@@ -8460,7 +8462,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>2</v>
@@ -8480,7 +8482,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>2</v>
@@ -8500,7 +8502,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="38" t="s">
@@ -8519,7 +8521,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>2</v>
@@ -8559,7 +8561,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>2</v>
@@ -8579,7 +8581,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C19" s="38" t="s">
         <v>2</v>
@@ -8597,7 +8599,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C20" s="38" t="s">
         <v>2</v>
@@ -8617,7 +8619,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>2</v>
@@ -8634,10 +8636,10 @@
     </row>
     <row r="22" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="40" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>2</v>
@@ -8663,7 +8665,7 @@
     <row r="24" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="34"/>
       <c r="B24" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C24" s="36"/>
       <c r="D24" s="36"/>
@@ -8733,7 +8735,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -8743,7 +8745,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -8755,7 +8757,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -8766,7 +8768,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C3" s="38" t="s">
         <v>2</v>
@@ -8787,7 +8789,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>2</v>
@@ -8807,7 +8809,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -8827,7 +8829,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -8867,7 +8869,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -8887,7 +8889,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>2</v>
@@ -8907,7 +8909,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C10" s="39"/>
       <c r="D10" s="38" t="s">
@@ -8935,7 +8937,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F11" s="68">
         <v>2.1874999999999998E-3</v>
@@ -8946,7 +8948,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>2</v>
@@ -8966,7 +8968,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>2</v>
@@ -8986,7 +8988,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>2</v>
@@ -9006,7 +9008,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>2</v>
@@ -9023,10 +9025,10 @@
     </row>
     <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="40" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>2</v>
@@ -9052,7 +9054,7 @@
     <row r="18" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="34"/>
       <c r="B18" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C18" s="36"/>
       <c r="D18" s="36"/>
@@ -9111,7 +9113,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -9121,7 +9123,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -9133,7 +9135,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -9153,7 +9155,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F3" s="68">
         <v>2.1874999999999998E-3</v>
@@ -9164,7 +9166,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>2</v>
@@ -9184,7 +9186,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -9204,7 +9206,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -9224,7 +9226,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>2</v>
@@ -9245,7 +9247,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -9265,7 +9267,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>2</v>
@@ -9283,7 +9285,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>2</v>
@@ -9303,7 +9305,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C11" s="39"/>
       <c r="D11" s="38" t="s">
@@ -9342,7 +9344,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>2</v>
@@ -9368,7 +9370,7 @@
     <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34"/>
       <c r="B15" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C15" s="36"/>
       <c r="D15" s="36"/>
@@ -9420,7 +9422,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -9430,7 +9432,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -9442,7 +9444,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -9462,7 +9464,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F3" s="68">
         <v>2.1874999999999998E-3</v>
@@ -9473,7 +9475,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>2</v>
@@ -9493,7 +9495,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -9513,7 +9515,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -9533,7 +9535,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>2</v>
@@ -9553,7 +9555,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -9573,7 +9575,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>2</v>
@@ -9614,7 +9616,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>2</v>
@@ -9635,7 +9637,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>2</v>
@@ -9656,7 +9658,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>2</v>
@@ -9674,7 +9676,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>2</v>
@@ -9683,7 +9685,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F14" s="68">
         <v>3.2291666666666666E-3</v>
@@ -9694,7 +9696,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>2</v>
@@ -9714,16 +9716,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="25" t="s">
         <v>112</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>114</v>
       </c>
       <c r="F16" s="68">
         <f>VLOOKUP(B16,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
@@ -9735,7 +9737,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C17" s="39"/>
       <c r="D17" s="38" t="s">
@@ -9754,7 +9756,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>2</v>
@@ -9763,7 +9765,7 @@
         <v>3</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F18" s="68">
         <f>VLOOKUP(B18,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
@@ -9775,7 +9777,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="38" t="s">
         <v>2</v>
@@ -9796,7 +9798,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C20" s="38" t="s">
         <v>2</v>
@@ -9816,7 +9818,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>2</v>
@@ -9836,7 +9838,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>2</v>
@@ -9877,7 +9879,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C24" s="38" t="s">
         <v>2</v>
@@ -9897,7 +9899,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C25" s="38" t="s">
         <v>2</v>
@@ -9917,7 +9919,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C26" s="38" t="s">
         <v>2</v>
@@ -9937,7 +9939,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C27" s="38" t="s">
         <v>2</v>
@@ -9957,7 +9959,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C28" s="38" t="s">
         <v>2</v>
@@ -9984,7 +9986,7 @@
     <row r="30" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="34"/>
       <c r="B30" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C30" s="36"/>
       <c r="D30" s="36"/>
@@ -10054,10 +10056,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.1640625" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
@@ -10072,7 +10074,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="2" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -10088,54 +10090,54 @@
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="59" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="D2" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="E2" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="F2" s="60" t="s">
         <v>135</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="G2" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="H2" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="G2" s="59" t="s">
+      <c r="I2" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="J2" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="I2" s="59" t="s">
+      <c r="K2" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="J2" s="59" t="s">
+      <c r="L2" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="K2" s="61" t="s">
+    </row>
+    <row r="3" spans="1:12" ht="22" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="118" t="s">
         <v>142</v>
       </c>
-      <c r="L2" s="59" t="s">
+      <c r="B3" s="18" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="22" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="C3" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="D3" s="13" t="s">
         <v>145</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>147</v>
       </c>
       <c r="E3" s="13">
         <v>10</v>
@@ -10149,17 +10151,17 @@
       <c r="L3" s="13"/>
     </row>
     <row r="4" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="80" t="s">
+      <c r="A4" s="118" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="D4" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>151</v>
       </c>
       <c r="E4" s="14">
         <v>11</v>
@@ -10173,14 +10175,14 @@
       <c r="L4" s="14"/>
     </row>
     <row r="5" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="80" t="s">
-        <v>152</v>
+      <c r="A5" s="118" t="s">
+        <v>150</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14">
@@ -10188,10 +10190,10 @@
       </c>
       <c r="F5" s="19"/>
       <c r="G5" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
@@ -10199,27 +10201,27 @@
       <c r="L5" s="14"/>
     </row>
     <row r="6" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="118" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>155</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>157</v>
       </c>
       <c r="E6" s="14">
         <v>11</v>
       </c>
       <c r="F6" s="19"/>
       <c r="G6" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14"/>
@@ -10229,14 +10231,14 @@
       <c r="L6" s="14"/>
     </row>
     <row r="7" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="80" t="s">
-        <v>160</v>
+      <c r="A7" s="118" t="s">
+        <v>158</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14">
@@ -10244,10 +10246,10 @@
       </c>
       <c r="F7" s="19"/>
       <c r="G7" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
@@ -10255,17 +10257,17 @@
       <c r="L7" s="14"/>
     </row>
     <row r="8" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="80" t="s">
-        <v>161</v>
+      <c r="A8" s="118" t="s">
+        <v>159</v>
       </c>
       <c r="B8" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>145</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>147</v>
       </c>
       <c r="E8" s="14">
         <v>26</v>
@@ -10279,27 +10281,27 @@
       <c r="L8" s="14"/>
     </row>
     <row r="9" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="80" t="s">
-        <v>162</v>
+      <c r="A9" s="118" t="s">
+        <v>160</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E9" s="14">
         <v>11</v>
       </c>
       <c r="F9" s="19"/>
       <c r="G9" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
@@ -10307,17 +10309,17 @@
       <c r="L9" s="14"/>
     </row>
     <row r="10" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="80" t="s">
-        <v>164</v>
+      <c r="A10" s="118" t="s">
+        <v>162</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>151</v>
       </c>
       <c r="E10" s="14">
         <v>13</v>
@@ -10331,14 +10333,14 @@
       <c r="L10" s="14"/>
     </row>
     <row r="11" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="80" t="s">
-        <v>165</v>
+      <c r="A11" s="118" t="s">
+        <v>163</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="14">
@@ -10346,10 +10348,10 @@
       </c>
       <c r="F11" s="19"/>
       <c r="G11" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
@@ -10357,14 +10359,14 @@
       <c r="L11" s="14"/>
     </row>
     <row r="12" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="80" t="s">
-        <v>166</v>
+      <c r="A12" s="118" t="s">
+        <v>164</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14">
@@ -10379,17 +10381,17 @@
       <c r="L12" s="14"/>
     </row>
     <row r="13" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="80" t="s">
-        <v>168</v>
+      <c r="A13" s="118" t="s">
+        <v>166</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>145</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>147</v>
       </c>
       <c r="E13" s="14">
         <v>14</v>
@@ -10403,41 +10405,41 @@
       <c r="L13" s="14"/>
     </row>
     <row r="14" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="89" t="s">
-        <v>169</v>
+      <c r="A14" s="119" t="s">
+        <v>167</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="19"/>
       <c r="G14" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
       <c r="K14" s="63"/>
       <c r="L14" s="14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="118" t="s">
+        <v>172</v>
+      </c>
+      <c r="B15" s="19" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="80" t="s">
+      <c r="C15" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="D15" s="14" t="s">
         <v>175</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>177</v>
       </c>
       <c r="E15" s="14">
         <v>13</v>
@@ -10446,29 +10448,29 @@
         <v>60</v>
       </c>
       <c r="G15" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="I15" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="J15" s="14" t="s">
         <v>179</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>181</v>
       </c>
       <c r="K15" s="63"/>
       <c r="L15" s="14"/>
     </row>
     <row r="16" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="80" t="s">
-        <v>182</v>
+      <c r="A16" s="118" t="s">
+        <v>180</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14">
@@ -10476,10 +10478,10 @@
       </c>
       <c r="F16" s="19"/>
       <c r="G16" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
@@ -10487,17 +10489,17 @@
       <c r="L16" s="14"/>
     </row>
     <row r="17" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="80" t="s">
-        <v>185</v>
+      <c r="A17" s="118" t="s">
+        <v>183</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E17" s="14">
         <v>10</v>
@@ -10513,17 +10515,17 @@
       <c r="L17" s="14"/>
     </row>
     <row r="18" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="80" t="s">
-        <v>187</v>
+      <c r="A18" s="118" t="s">
+        <v>185</v>
       </c>
       <c r="B18" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>151</v>
       </c>
       <c r="E18" s="14">
         <v>16</v>
@@ -10539,17 +10541,17 @@
       <c r="L18" s="14"/>
     </row>
     <row r="19" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="80" t="s">
-        <v>188</v>
+      <c r="A19" s="118" t="s">
+        <v>186</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E19" s="14">
         <v>16</v>
@@ -10558,48 +10560,48 @@
         <v>75</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K19" s="63"/>
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="80" t="s">
-        <v>192</v>
+      <c r="A20" s="118" t="s">
+        <v>190</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E20" s="14"/>
       <c r="F20" s="19">
         <v>120</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K20" s="63">
         <v>150</v>
@@ -10607,25 +10609,25 @@
       <c r="L20" s="14"/>
     </row>
     <row r="21" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="80">
+      <c r="A21" s="120">
         <v>46194</v>
       </c>
-      <c r="B21" s="81">
+      <c r="B21" s="80">
         <v>0.70833333333333337</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="19"/>
       <c r="G21" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14"/>
@@ -10633,23 +10635,23 @@
       <c r="L21" s="14"/>
     </row>
     <row r="22" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="80">
+      <c r="A22" s="120">
         <v>46197</v>
       </c>
-      <c r="B22" s="81">
+      <c r="B22" s="80">
         <v>0.75</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="19"/>
       <c r="G22" s="14" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14"/>
@@ -10657,7 +10659,28 @@
       <c r="L22" s="14"/>
     </row>
     <row r="23" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="90"/>
+      <c r="A23" s="121"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="1"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" s="1"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" s="1"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -10700,7 +10723,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -10710,7 +10733,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -10722,7 +10745,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -10742,7 +10765,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F3" s="68">
         <v>2.1874999999999998E-3</v>
@@ -10753,7 +10776,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>2</v>
@@ -10773,7 +10796,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -10793,7 +10816,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -10813,7 +10836,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>2</v>
@@ -10833,7 +10856,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -10853,7 +10876,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>2</v>
@@ -10894,7 +10917,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>2</v>
@@ -10915,7 +10938,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>2</v>
@@ -10933,7 +10956,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>2</v>
@@ -10942,7 +10965,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F13" s="68">
         <v>3.2291666666666666E-3</v>
@@ -10953,16 +10976,16 @@
         <v>1</v>
       </c>
       <c r="B14" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="25" t="s">
         <v>112</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>114</v>
       </c>
       <c r="F14" s="68">
         <f>VLOOKUP(B14,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
@@ -10974,7 +10997,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="38" t="s">
@@ -10993,7 +11016,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>2</v>
@@ -11013,7 +11036,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>2</v>
@@ -11054,7 +11077,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C19" s="38" t="s">
         <v>2</v>
@@ -11074,7 +11097,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C20" s="38" t="s">
         <v>2</v>
@@ -11094,7 +11117,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>2</v>
@@ -11114,7 +11137,7 @@
         <v>9</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>2</v>
@@ -11134,7 +11157,7 @@
         <v>10</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>2</v>
@@ -11160,7 +11183,7 @@
     <row r="25" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34"/>
       <c r="B25" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C25" s="36"/>
       <c r="D25" s="36"/>
@@ -11232,7 +11255,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -11242,7 +11265,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -11254,7 +11277,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -11274,7 +11297,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F3" s="68">
         <v>2.1874999999999998E-3</v>
@@ -11285,7 +11308,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>2</v>
@@ -11305,7 +11328,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -11325,7 +11348,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -11345,7 +11368,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>2</v>
@@ -11365,7 +11388,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -11385,7 +11408,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>2</v>
@@ -11405,7 +11428,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>2</v>
@@ -11414,7 +11437,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F10" s="68">
         <v>3.2291666666666666E-3</v>
@@ -11425,7 +11448,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>2</v>
@@ -11446,7 +11469,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>2</v>
@@ -11466,7 +11489,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>2</v>
@@ -11492,7 +11515,7 @@
     <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34"/>
       <c r="B15" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C15" s="36"/>
       <c r="D15" s="36"/>
@@ -11546,7 +11569,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -11556,7 +11579,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -11568,7 +11591,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -11588,7 +11611,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F3" s="68">
         <v>2.1874999999999998E-3</v>
@@ -11599,7 +11622,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>2</v>
@@ -11619,7 +11642,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -11639,7 +11662,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -11659,7 +11682,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>2</v>
@@ -11679,7 +11702,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -11699,7 +11722,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>2</v>
@@ -11719,7 +11742,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>2</v>
@@ -11739,7 +11762,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>2</v>
@@ -11760,7 +11783,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>2</v>
@@ -11798,7 +11821,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>2</v>
@@ -11818,7 +11841,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>2</v>
@@ -11838,7 +11861,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>2</v>
@@ -11858,7 +11881,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>2</v>
@@ -11867,7 +11890,7 @@
         <v>3</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F17" s="68">
         <v>3.2291666666666666E-3</v>
@@ -11878,7 +11901,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>2</v>
@@ -11904,7 +11927,7 @@
     <row r="20" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="34"/>
       <c r="B20" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C20" s="36"/>
       <c r="D20" s="36"/>
@@ -11967,7 +11990,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -11977,7 +12000,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -11989,7 +12012,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -12009,7 +12032,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F3" s="68">
         <v>2.1874999999999998E-3</v>
@@ -12020,7 +12043,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>2</v>
@@ -12040,7 +12063,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -12060,7 +12083,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -12080,7 +12103,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>2</v>
@@ -12101,7 +12124,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -12122,7 +12145,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>2</v>
@@ -12142,7 +12165,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>2</v>
@@ -12162,7 +12185,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>2</v>
@@ -12182,7 +12205,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>2</v>
@@ -12202,7 +12225,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>2</v>
@@ -12228,7 +12251,7 @@
     <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34"/>
       <c r="B15" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C15" s="36"/>
       <c r="D15" s="36"/>
@@ -12282,7 +12305,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -12292,7 +12315,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -12304,7 +12327,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -12324,7 +12347,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F3" s="68">
         <v>2.1874999999999998E-3</v>
@@ -12335,7 +12358,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>2</v>
@@ -12355,7 +12378,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -12376,7 +12399,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -12417,7 +12440,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -12437,7 +12460,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C9" s="39"/>
       <c r="D9" s="38" t="s">
@@ -12456,7 +12479,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>2</v>
@@ -12476,7 +12499,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>2</v>
@@ -12496,7 +12519,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>2</v>
@@ -12522,7 +12545,7 @@
     <row r="14" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34"/>
       <c r="B14" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C14" s="36"/>
       <c r="D14" s="36"/>
@@ -12574,7 +12597,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="11" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="52" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -12586,96 +12609,96 @@
     </row>
     <row r="2" spans="1:8" s="11" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="54" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="D2" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="E2" s="54" t="s">
         <v>202</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="F2" s="54" t="s">
         <v>203</v>
-      </c>
-      <c r="E2" s="54" t="s">
-        <v>204</v>
-      </c>
-      <c r="F2" s="54" t="s">
-        <v>205</v>
       </c>
       <c r="G2" s="54"/>
       <c r="H2" s="54"/>
     </row>
     <row r="3" spans="1:8" ht="20" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>210</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>212</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>40</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G4" s="17"/>
       <c r="H4" s="17"/>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>36</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="17" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>36</v>
@@ -12684,26 +12707,26 @@
         <v>40</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="17" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
@@ -12750,7 +12773,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="55" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B1" s="56"/>
       <c r="C1" s="56"/>
@@ -12761,69 +12784,69 @@
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B2" s="57" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="D2" s="57" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="E2" s="57" t="s">
         <v>227</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="F2" s="57" t="s">
         <v>228</v>
       </c>
-      <c r="E2" s="57" t="s">
-        <v>229</v>
-      </c>
-      <c r="F2" s="57" t="s">
-        <v>230</v>
-      </c>
       <c r="G2" s="57" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="22" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="D3" s="13" t="s">
         <v>232</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>234</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="D4" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="E4" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="14" t="s">
         <v>239</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -12846,7 +12869,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -12858,19 +12881,19 @@
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="64" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B2" s="64" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2" s="64" t="s">
         <v>243</v>
       </c>
-      <c r="C2" s="64" t="s">
-        <v>244</v>
-      </c>
-      <c r="D2" s="64" t="s">
-        <v>245</v>
-      </c>
       <c r="E2" s="64" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F2" s="43"/>
       <c r="G2" s="43"/>
@@ -12881,7 +12904,7 @@
         <v>46154</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>31</v>
@@ -12890,7 +12913,7 @@
         <v>86.99</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F3" s="17"/>
       <c r="G3" s="17"/>
@@ -13159,7 +13182,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -13169,7 +13192,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -13181,7 +13204,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -13198,7 +13221,7 @@
     <row r="4" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="34"/>
       <c r="B4" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C4" s="36"/>
       <c r="D4" s="36"/>
@@ -13228,7 +13251,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="30"/>
@@ -13238,7 +13261,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -13250,7 +13273,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>6</v>
@@ -13267,7 +13290,7 @@
     <row r="4" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="34"/>
       <c r="B4" s="35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C4" s="36"/>
       <c r="D4" s="36"/>
@@ -13296,574 +13319,574 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="109" t="s">
+        <v>251</v>
+      </c>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="111"/>
+    </row>
+    <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="83" t="s">
+        <v>247</v>
+      </c>
+      <c r="B2" s="84" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="84" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="84" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="84" t="s">
+        <v>248</v>
+      </c>
+      <c r="F2" s="85" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="86">
+        <v>1</v>
+      </c>
+      <c r="B3" s="87" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="88" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="89" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="87" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="90">
+        <v>2.1875000000000002E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="91">
+        <v>2</v>
+      </c>
+      <c r="B4" s="92" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="92" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="82">
+        <v>2.2569444444444399E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="91">
+        <v>3</v>
+      </c>
+      <c r="B5" s="92" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="92" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="82">
+        <v>2.5810185185185198E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="91">
+        <v>4</v>
+      </c>
+      <c r="B6" s="92" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="92" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="82">
+        <v>2.0833333333333298E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="91">
+        <v>5</v>
+      </c>
+      <c r="B7" s="92" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="92" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="82">
+        <v>2.04861111111111E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="91">
+        <v>6</v>
+      </c>
+      <c r="B8" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="92" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="82">
+        <v>3.4143518518518498E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="91">
+        <v>7</v>
+      </c>
+      <c r="B9" s="92" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="92" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="82">
+        <v>2.48842592592593E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="91">
+        <v>8</v>
+      </c>
+      <c r="B10" s="92" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="92" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="82">
+        <v>3.59953703703704E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="91">
+        <v>9</v>
+      </c>
+      <c r="B11" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="92" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="82">
+        <v>2.0949074074074099E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="91">
+        <v>10</v>
+      </c>
+      <c r="B12" s="92" t="s">
+        <v>252</v>
+      </c>
+      <c r="C12" s="95" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="96" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="92" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="82">
+        <v>2.5810185185185198E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="91">
+        <v>11</v>
+      </c>
+      <c r="B13" s="92" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="92" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="82">
+        <v>2.8587962962962998E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="91">
+        <v>12</v>
+      </c>
+      <c r="B14" s="92" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="92" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="82">
+        <v>2.4305555555555599E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="91">
+        <v>13</v>
+      </c>
+      <c r="B15" s="92" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="92" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="82">
+        <v>3.04398148148148E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="91">
+        <v>14</v>
+      </c>
+      <c r="B16" s="92" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="92" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="82">
+        <v>3.32175925925926E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="112" t="s">
         <v>253</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="85"/>
-    </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
+      <c r="B17" s="113"/>
+      <c r="C17" s="113"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="114"/>
+    </row>
+    <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="91">
+        <v>15</v>
+      </c>
+      <c r="B18" s="92" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="97" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="98" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="92" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="82">
+        <v>2.71990740740741E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="99">
+        <v>16</v>
+      </c>
+      <c r="B19" s="92" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="92" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="82">
+        <v>2.7893518518518502E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="100">
+        <v>17</v>
+      </c>
+      <c r="B20" s="92" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="92" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="82">
+        <v>3.3680555555555599E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="91">
+        <v>18</v>
+      </c>
+      <c r="B21" s="92" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="92" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="82">
+        <v>2.9513888888888901E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="91">
+        <v>19</v>
+      </c>
+      <c r="B22" s="92" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="92" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="82">
+        <v>2.60416666666667E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="91">
+        <v>20</v>
+      </c>
+      <c r="B23" s="92" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="92" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="82">
+        <v>3.2291666666666701E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="91">
+        <v>21</v>
+      </c>
+      <c r="B24" s="92" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="92" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="101">
+        <v>2.7430555555555602E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="91">
+        <v>22</v>
+      </c>
+      <c r="B25" s="92" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="92" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="82">
+        <v>2.60416666666667E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="91">
+        <v>23</v>
+      </c>
+      <c r="B26" s="92" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="92" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="82">
+        <v>1.9791666666666699E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="91">
+        <v>24</v>
+      </c>
+      <c r="B27" s="92" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="92" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="82">
+        <v>2.6504629629629599E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="91">
+        <v>25</v>
+      </c>
+      <c r="B28" s="105" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="106" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="107" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="105" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="108">
+        <v>4.6874999999999998E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="91">
+        <v>26</v>
+      </c>
+      <c r="B29" s="92" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="94" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="92" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" s="82">
+        <v>5.9606481481481498E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="102"/>
+      <c r="B30" s="103" t="s">
         <v>249</v>
       </c>
-      <c r="B2" s="93" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="93" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="93" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="93" t="s">
-        <v>250</v>
-      </c>
-      <c r="F2" s="94" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="95">
-        <v>1</v>
-      </c>
-      <c r="B3" s="96" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="97" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="98" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="96" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="99">
-        <v>2.1875000000000002E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="100">
-        <v>2</v>
-      </c>
-      <c r="B4" s="101" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="101" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="91">
-        <v>2.2569444444444399E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="100">
-        <v>3</v>
-      </c>
-      <c r="B5" s="101" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="101" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="91">
-        <v>2.5810185185185198E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="100">
-        <v>4</v>
-      </c>
-      <c r="B6" s="101" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="101" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="91">
-        <v>2.0833333333333298E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="100">
-        <v>5</v>
-      </c>
-      <c r="B7" s="101" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="101" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="91">
-        <v>2.04861111111111E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="100">
-        <v>6</v>
-      </c>
-      <c r="B8" s="101" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="101" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="91">
-        <v>3.4143518518518498E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="100">
-        <v>7</v>
-      </c>
-      <c r="B9" s="101" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="101" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="91">
-        <v>2.48842592592593E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="100">
-        <v>8</v>
-      </c>
-      <c r="B10" s="101" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="101" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="91">
-        <v>3.59953703703704E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="100">
-        <v>9</v>
-      </c>
-      <c r="B11" s="101" t="s">
-        <v>129</v>
-      </c>
-      <c r="C11" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="101" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="91">
-        <v>2.0949074074074099E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="100">
-        <v>10</v>
-      </c>
-      <c r="B12" s="101" t="s">
-        <v>254</v>
-      </c>
-      <c r="C12" s="104" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="105" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="101" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="91">
-        <v>2.5810185185185198E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="100">
-        <v>11</v>
-      </c>
-      <c r="B13" s="101" t="s">
-        <v>92</v>
-      </c>
-      <c r="C13" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="101" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="91">
-        <v>2.8587962962962998E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="100">
-        <v>12</v>
-      </c>
-      <c r="B14" s="101" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="101" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="91">
-        <v>2.4305555555555599E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="100">
-        <v>13</v>
-      </c>
-      <c r="B15" s="101" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="101" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="91">
-        <v>3.04398148148148E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="100">
-        <v>14</v>
-      </c>
-      <c r="B16" s="101" t="s">
-        <v>125</v>
-      </c>
-      <c r="C16" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="101" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" s="91">
-        <v>3.32175925925926E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="111" t="s">
-        <v>255</v>
-      </c>
-      <c r="B17" s="112"/>
-      <c r="C17" s="112"/>
-      <c r="D17" s="112"/>
-      <c r="E17" s="112"/>
-      <c r="F17" s="113"/>
-    </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="100">
-        <v>15</v>
-      </c>
-      <c r="B18" s="101" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="106" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="107" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="101" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="91">
-        <v>2.71990740740741E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="108">
-        <v>16</v>
-      </c>
-      <c r="B19" s="101" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="101" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="91">
-        <v>2.7893518518518502E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="109">
-        <v>17</v>
-      </c>
-      <c r="B20" s="101" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="101" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="91">
-        <v>3.3680555555555599E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="100">
-        <v>18</v>
-      </c>
-      <c r="B21" s="101" t="s">
-        <v>101</v>
-      </c>
-      <c r="C21" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="101" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" s="91">
-        <v>2.9513888888888901E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="100">
-        <v>19</v>
-      </c>
-      <c r="B22" s="101" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="101" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="91">
-        <v>2.60416666666667E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="100">
-        <v>20</v>
-      </c>
-      <c r="B23" s="101" t="s">
-        <v>99</v>
-      </c>
-      <c r="C23" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="101" t="s">
-        <v>50</v>
-      </c>
-      <c r="F23" s="91">
-        <v>3.2291666666666701E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="100">
-        <v>21</v>
-      </c>
-      <c r="B24" s="101" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="101" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" s="110">
-        <v>2.7430555555555602E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="100">
-        <v>22</v>
-      </c>
-      <c r="B25" s="101" t="s">
-        <v>110</v>
-      </c>
-      <c r="C25" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25" s="101" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" s="91">
-        <v>2.60416666666667E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="100">
-        <v>23</v>
-      </c>
-      <c r="B26" s="101" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E26" s="101" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" s="91">
-        <v>1.9791666666666699E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="100">
-        <v>24</v>
-      </c>
-      <c r="B27" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="101" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" s="91">
-        <v>2.6504629629629599E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="100">
-        <v>25</v>
-      </c>
-      <c r="B28" s="117" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="118" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="119" t="s">
-        <v>3</v>
-      </c>
-      <c r="E28" s="117" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" s="120">
-        <v>4.6874999999999998E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="100">
-        <v>26</v>
-      </c>
-      <c r="B29" s="101" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="101" t="s">
-        <v>31</v>
-      </c>
-      <c r="F29" s="91">
-        <v>5.9606481481481498E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="114"/>
-      <c r="B30" s="115" t="s">
-        <v>251</v>
-      </c>
-      <c r="C30" s="115"/>
-      <c r="D30" s="115"/>
-      <c r="E30" s="115"/>
-      <c r="F30" s="116">
+      <c r="C30" s="103"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="104">
         <f>SUM(F3:F16,F18:F29)</f>
         <v>7.5277777777777805E-2</v>
       </c>
@@ -13873,7 +13896,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
   </mergeCells>
-  <conditionalFormatting sqref="A16:A17 B16:F16 A28 A18:F27 A3:F15 A29:F30">
+  <conditionalFormatting sqref="A3:F15 B16:F16 A16:A17 A18:F27 A28 A29:F30">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -13953,18 +13976,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="86" t="s">
-        <v>274</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="88"/>
+      <c r="A1" s="115" t="s">
+        <v>272</v>
+      </c>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="117"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="70" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>1</v>
@@ -13976,7 +13999,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F2" s="71" t="s">
         <v>6</v>
@@ -13996,7 +14019,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F3" s="73">
         <v>2.1874999999999998E-3</v>
@@ -14007,7 +14030,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>2</v>
@@ -14027,7 +14050,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>2</v>
@@ -14047,7 +14070,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>2</v>
@@ -14067,7 +14090,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>2</v>
@@ -14087,7 +14110,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>2</v>
@@ -14127,7 +14150,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>2</v>
@@ -14146,7 +14169,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>2</v>
@@ -14166,7 +14189,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>2</v>
@@ -14186,7 +14209,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>2</v>
@@ -14206,7 +14229,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>2</v>
@@ -14226,7 +14249,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>2</v>
@@ -14246,7 +14269,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>2</v>
@@ -14266,7 +14289,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>2</v>
@@ -14286,7 +14309,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>2</v>
@@ -14312,7 +14335,7 @@
     <row r="20" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="76"/>
       <c r="B20" s="77" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C20" s="78"/>
       <c r="D20" s="78"/>

--- a/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings website/rock/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF8BC667-0129-D640-BB06-69033851BFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98941BBB-016E-904C-87C4-876AAFC79C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3280" yWindow="2580" windowWidth="30620" windowHeight="18100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3260" yWindow="2560" windowWidth="30620" windowHeight="18100" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -2024,6 +2024,18 @@
     <xf numFmtId="165" fontId="3" fillId="4" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2050,18 +2062,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2097,10 +2097,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10127,7 +10123,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="22" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="109" t="s">
         <v>142</v>
       </c>
       <c r="B3" s="18" t="s">
@@ -10151,7 +10147,7 @@
       <c r="L3" s="13"/>
     </row>
     <row r="4" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="109" t="s">
         <v>146</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -10175,7 +10171,7 @@
       <c r="L4" s="14"/>
     </row>
     <row r="5" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="118" t="s">
+      <c r="A5" s="109" t="s">
         <v>150</v>
       </c>
       <c r="B5" s="19" t="s">
@@ -10201,7 +10197,7 @@
       <c r="L5" s="14"/>
     </row>
     <row r="6" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="109" t="s">
         <v>153</v>
       </c>
       <c r="B6" s="19" t="s">
@@ -10231,7 +10227,7 @@
       <c r="L6" s="14"/>
     </row>
     <row r="7" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="118" t="s">
+      <c r="A7" s="109" t="s">
         <v>158</v>
       </c>
       <c r="B7" s="19" t="s">
@@ -10257,7 +10253,7 @@
       <c r="L7" s="14"/>
     </row>
     <row r="8" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="118" t="s">
+      <c r="A8" s="109" t="s">
         <v>159</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -10281,7 +10277,7 @@
       <c r="L8" s="14"/>
     </row>
     <row r="9" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="109" t="s">
         <v>160</v>
       </c>
       <c r="B9" s="19" t="s">
@@ -10309,7 +10305,7 @@
       <c r="L9" s="14"/>
     </row>
     <row r="10" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="118" t="s">
+      <c r="A10" s="109" t="s">
         <v>162</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -10333,7 +10329,7 @@
       <c r="L10" s="14"/>
     </row>
     <row r="11" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="118" t="s">
+      <c r="A11" s="109" t="s">
         <v>163</v>
       </c>
       <c r="B11" s="19" t="s">
@@ -10359,7 +10355,7 @@
       <c r="L11" s="14"/>
     </row>
     <row r="12" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="118" t="s">
+      <c r="A12" s="109" t="s">
         <v>164</v>
       </c>
       <c r="B12" s="19" t="s">
@@ -10381,7 +10377,7 @@
       <c r="L12" s="14"/>
     </row>
     <row r="13" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="118" t="s">
+      <c r="A13" s="109" t="s">
         <v>166</v>
       </c>
       <c r="B13" s="19" t="s">
@@ -10405,7 +10401,7 @@
       <c r="L13" s="14"/>
     </row>
     <row r="14" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="119" t="s">
+      <c r="A14" s="110" t="s">
         <v>167</v>
       </c>
       <c r="B14" s="19"/>
@@ -10429,7 +10425,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="109" t="s">
         <v>172</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -10463,7 +10459,7 @@
       <c r="L15" s="14"/>
     </row>
     <row r="16" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="118" t="s">
+      <c r="A16" s="109" t="s">
         <v>180</v>
       </c>
       <c r="B16" s="19" t="s">
@@ -10489,7 +10485,7 @@
       <c r="L16" s="14"/>
     </row>
     <row r="17" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="118" t="s">
+      <c r="A17" s="109" t="s">
         <v>183</v>
       </c>
       <c r="B17" s="19" t="s">
@@ -10515,7 +10511,7 @@
       <c r="L17" s="14"/>
     </row>
     <row r="18" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="118" t="s">
+      <c r="A18" s="109" t="s">
         <v>185</v>
       </c>
       <c r="B18" s="19" t="s">
@@ -10541,7 +10537,7 @@
       <c r="L18" s="14"/>
     </row>
     <row r="19" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="118" t="s">
+      <c r="A19" s="109" t="s">
         <v>186</v>
       </c>
       <c r="B19" s="19" t="s">
@@ -10575,7 +10571,7 @@
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="118" t="s">
+      <c r="A20" s="109" t="s">
         <v>190</v>
       </c>
       <c r="B20" s="19" t="s">
@@ -10609,7 +10605,7 @@
       <c r="L20" s="14"/>
     </row>
     <row r="21" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="120">
+      <c r="A21" s="111">
         <v>46194</v>
       </c>
       <c r="B21" s="80">
@@ -10635,7 +10631,7 @@
       <c r="L21" s="14"/>
     </row>
     <row r="22" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="120">
+      <c r="A22" s="111">
         <v>46197</v>
       </c>
       <c r="B22" s="80">
@@ -10659,7 +10655,7 @@
       <c r="L22" s="14"/>
     </row>
     <row r="23" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="121"/>
+      <c r="A23" s="112"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
@@ -13314,19 +13310,19 @@
     <col min="1" max="1" width="4.83203125" style="20" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="7.5" style="20" customWidth="1"/>
-    <col min="5" max="5" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1640625" style="20" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" style="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="113" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="111"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="115"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="83" t="s">
@@ -13629,14 +13625,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="112" t="s">
+      <c r="A17" s="116" t="s">
         <v>253</v>
       </c>
-      <c r="B17" s="113"/>
-      <c r="C17" s="113"/>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="114"/>
+      <c r="B17" s="117"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="118"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="91">
@@ -13976,14 +13972,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="119" t="s">
         <v>272</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="117"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="121"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="70" t="s">
